--- a/reference/verification/Labourmax_verification.xlsx
+++ b/reference/verification/Labourmax_verification.xlsx
@@ -527,7 +527,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>THIS WORKBOOK IS A WORK AID AND NEVER A SOURCE OF TRUTH. The fixtures in reference/ are the loaded data and docs/DECISIONS.md is the register; importverification records that a figure was checked and can never change one.</t>
+          <t>THIS WORKBOOK IS A WORK AID AND NEVER A SOURCE OF TRUTH. The fixtures in reference/ are the loaded data and docs/DECISIONS.md is the register; importverification records that a figure was checked and can never change one. The file itself is DISPOSABLE - every imported tick is in the database and is pre-filled on the next export. The counts below are as at export.</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,14 @@
       <c r="B6" t="n">
         <v>23</v>
       </c>
-      <c r="C6">
-        <f>COUNTIFS(Figures!$A:$A,$A6,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D6">
-        <f>COUNTIFS(Figures!$A:$A,$A6,Figures!$K:$K,"QUERY")</f>
-        <v/>
-      </c>
-      <c r="E6">
-        <f>$B6-$C6-$D6</f>
-        <v/>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -596,17 +593,14 @@
       <c r="B7" t="n">
         <v>67</v>
       </c>
-      <c r="C7">
-        <f>COUNTIFS(Figures!$A:$A,$A7,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D7">
-        <f>COUNTIFS(Figures!$A:$A,$A7,Figures!$K:$K,"QUERY")</f>
-        <v/>
-      </c>
-      <c r="E7">
-        <f>$B7-$C7-$D7</f>
-        <v/>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="8">
@@ -618,17 +612,14 @@
       <c r="B8" t="n">
         <v>86</v>
       </c>
-      <c r="C8">
-        <f>COUNTIFS(Figures!$A:$A,$A8,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D8">
-        <f>COUNTIFS(Figures!$A:$A,$A8,Figures!$K:$K,"QUERY")</f>
-        <v/>
-      </c>
-      <c r="E8">
-        <f>$B8-$C8-$D8</f>
-        <v/>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="9">
@@ -640,17 +631,14 @@
       <c r="B9" t="n">
         <v>2</v>
       </c>
-      <c r="C9">
-        <f>COUNTIFS(Figures!$A:$A,$A9,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D9">
-        <f>COUNTIFS(Figures!$A:$A,$A9,Figures!$K:$K,"QUERY")</f>
-        <v/>
-      </c>
-      <c r="E9">
-        <f>$B9-$C9-$D9</f>
-        <v/>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -662,17 +650,14 @@
       <c r="B10" t="n">
         <v>2</v>
       </c>
-      <c r="C10">
-        <f>COUNTIFS(Figures!$A:$A,$A10,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D10">
-        <f>COUNTIFS(Figures!$A:$A,$A10,Figures!$K:$K,"QUERY")</f>
-        <v/>
-      </c>
-      <c r="E10">
-        <f>$B10-$C10-$D10</f>
-        <v/>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -684,17 +669,14 @@
       <c r="B11" t="n">
         <v>2</v>
       </c>
-      <c r="C11">
-        <f>COUNTIFS(Figures!$A:$A,$A11,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D11">
-        <f>COUNTIFS(Figures!$A:$A,$A11,Figures!$K:$K,"QUERY")</f>
-        <v/>
-      </c>
-      <c r="E11">
-        <f>$B11-$C11-$D11</f>
-        <v/>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -706,17 +688,14 @@
       <c r="B12" t="n">
         <v>2</v>
       </c>
-      <c r="C12">
-        <f>COUNTIFS(Figures!$A:$A,$A12,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D12">
-        <f>COUNTIFS(Figures!$A:$A,$A12,Figures!$K:$K,"QUERY")</f>
-        <v/>
-      </c>
-      <c r="E12">
-        <f>$B12-$C12-$D12</f>
-        <v/>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -728,17 +707,14 @@
       <c r="B13" t="n">
         <v>8</v>
       </c>
-      <c r="C13">
-        <f>COUNTIFS(Figures!$A:$A,$A13,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D13">
-        <f>COUNTIFS(Figures!$A:$A,$A13,Figures!$K:$K,"QUERY")</f>
-        <v/>
-      </c>
-      <c r="E13">
-        <f>$B13-$C13-$D13</f>
-        <v/>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -750,17 +726,14 @@
       <c r="B14" t="n">
         <v>75</v>
       </c>
-      <c r="C14">
-        <f>COUNTIFS(Figures!$A:$A,$A14,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D14">
-        <f>COUNTIFS(Figures!$A:$A,$A14,Figures!$K:$K,"QUERY")</f>
-        <v/>
-      </c>
-      <c r="E14">
-        <f>$B14-$C14-$D14</f>
-        <v/>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="15">
@@ -772,17 +745,14 @@
       <c r="B15" t="n">
         <v>114</v>
       </c>
-      <c r="C15">
-        <f>COUNTIFS(Figures!$A:$A,$A15,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D15">
-        <f>COUNTIFS(Figures!$A:$A,$A15,Figures!$K:$K,"QUERY")</f>
-        <v/>
-      </c>
-      <c r="E15">
-        <f>$B15-$C15-$D15</f>
-        <v/>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -794,17 +764,14 @@
       <c r="B16" t="n">
         <v>3</v>
       </c>
-      <c r="C16">
-        <f>COUNTIFS(Figures!$A:$A,$A16,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D16">
-        <f>COUNTIFS(Figures!$A:$A,$A16,Figures!$K:$K,"QUERY")</f>
-        <v/>
-      </c>
-      <c r="E16">
-        <f>$B16-$C16-$D16</f>
-        <v/>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -816,17 +783,14 @@
       <c r="B17" t="n">
         <v>12</v>
       </c>
-      <c r="C17">
-        <f>COUNTIFS(Figures!$A:$A,$A17,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D17">
-        <f>COUNTIFS(Figures!$A:$A,$A17,Figures!$K:$K,"QUERY")</f>
-        <v/>
-      </c>
-      <c r="E17">
-        <f>$B17-$C17-$D17</f>
-        <v/>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -838,17 +802,14 @@
       <c r="B18" t="n">
         <v>36</v>
       </c>
-      <c r="C18">
-        <f>COUNTIFS(Figures!$A:$A,$A18,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D18">
-        <f>COUNTIFS(Figures!$A:$A,$A18,Figures!$K:$K,"QUERY")</f>
-        <v/>
-      </c>
-      <c r="E18">
-        <f>$B18-$C18-$D18</f>
-        <v/>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="19">
@@ -860,17 +821,14 @@
       <c r="B19" t="n">
         <v>67</v>
       </c>
-      <c r="C19">
-        <f>COUNTIFS(Figures!$A:$A,$A19,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D19">
-        <f>COUNTIFS(Figures!$A:$A,$A19,Figures!$K:$K,"QUERY")</f>
-        <v/>
-      </c>
-      <c r="E19">
-        <f>$B19-$C19-$D19</f>
-        <v/>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -882,17 +840,14 @@
       <c r="B20" t="n">
         <v>66</v>
       </c>
-      <c r="C20">
-        <f>COUNTIFS(Figures!$A:$A,$A20,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D20">
-        <f>COUNTIFS(Figures!$A:$A,$A20,Figures!$K:$K,"QUERY")</f>
-        <v/>
-      </c>
-      <c r="E20">
-        <f>$B20-$C20-$D20</f>
-        <v/>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="21">
@@ -904,17 +859,14 @@
       <c r="B21" t="n">
         <v>4</v>
       </c>
-      <c r="C21">
-        <f>COUNTIFS(Figures!$A:$A,$A21,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D21">
-        <f>COUNTIFS(Figures!$A:$A,$A21,Figures!$K:$K,"QUERY")</f>
-        <v/>
-      </c>
-      <c r="E21">
-        <f>$B21-$C21-$D21</f>
-        <v/>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -926,17 +878,14 @@
       <c r="B22" t="n">
         <v>4</v>
       </c>
-      <c r="C22">
-        <f>COUNTIFS(Figures!$A:$A,$A22,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D22">
-        <f>COUNTIFS(Figures!$A:$A,$A22,Figures!$K:$K,"QUERY")</f>
-        <v/>
-      </c>
-      <c r="E22">
-        <f>$B22-$C22-$D22</f>
-        <v/>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -948,17 +897,14 @@
       <c r="B23" t="n">
         <v>2</v>
       </c>
-      <c r="C23">
-        <f>COUNTIFS(Figures!$A:$A,$A23,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D23">
-        <f>COUNTIFS(Figures!$A:$A,$A23,Figures!$K:$K,"QUERY")</f>
-        <v/>
-      </c>
-      <c r="E23">
-        <f>$B23-$C23-$D23</f>
-        <v/>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -970,17 +916,14 @@
       <c r="B24" t="n">
         <v>7</v>
       </c>
-      <c r="C24">
-        <f>COUNTIFS(Figures!$A:$A,$A24,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D24">
-        <f>COUNTIFS(Figures!$A:$A,$A24,Figures!$K:$K,"QUERY")</f>
-        <v/>
-      </c>
-      <c r="E24">
-        <f>$B24-$C24-$D24</f>
-        <v/>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -992,17 +935,14 @@
       <c r="B25" s="6" t="n">
         <v>582</v>
       </c>
-      <c r="C25" s="6">
-        <f>SUM(C6:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="6">
-        <f>SUM(D6:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="6">
-        <f>SUM(E6:E24)</f>
-        <v/>
+      <c r="C25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>582</v>
       </c>
     </row>
     <row r="27">
@@ -1058,13 +998,11 @@
       <c r="B29" t="n">
         <v>0</v>
       </c>
-      <c r="C29">
-        <f>COUNTIFS(Figures!$D:$D,$A29,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D29">
-        <f>COUNTIFS(Figures!$D:$D,$A29,Figures!$K:$K,"QUERY")</f>
-        <v/>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1091,13 +1029,11 @@
       <c r="B30" t="n">
         <v>114</v>
       </c>
-      <c r="C30">
-        <f>COUNTIFS(Figures!$D:$D,$A30,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D30">
-        <f>COUNTIFS(Figures!$D:$D,$A30,Figures!$K:$K,"QUERY")</f>
-        <v/>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1124,13 +1060,11 @@
       <c r="B31" t="n">
         <v>2</v>
       </c>
-      <c r="C31">
-        <f>COUNTIFS(Figures!$D:$D,$A31,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D31">
-        <f>COUNTIFS(Figures!$D:$D,$A31,Figures!$K:$K,"QUERY")</f>
-        <v/>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1157,13 +1091,11 @@
       <c r="B32" t="n">
         <v>2</v>
       </c>
-      <c r="C32">
-        <f>COUNTIFS(Figures!$D:$D,$A32,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D32">
-        <f>COUNTIFS(Figures!$D:$D,$A32,Figures!$K:$K,"QUERY")</f>
-        <v/>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1190,13 +1122,11 @@
       <c r="B33" t="n">
         <v>2</v>
       </c>
-      <c r="C33">
-        <f>COUNTIFS(Figures!$D:$D,$A33,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D33">
-        <f>COUNTIFS(Figures!$D:$D,$A33,Figures!$K:$K,"QUERY")</f>
-        <v/>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1223,13 +1153,11 @@
       <c r="B34" t="n">
         <v>12</v>
       </c>
-      <c r="C34">
-        <f>COUNTIFS(Figures!$D:$D,$A34,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D34">
-        <f>COUNTIFS(Figures!$D:$D,$A34,Figures!$K:$K,"QUERY")</f>
-        <v/>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1256,13 +1184,11 @@
       <c r="B35" t="n">
         <v>54</v>
       </c>
-      <c r="C35">
-        <f>COUNTIFS(Figures!$D:$D,$A35,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D35">
-        <f>COUNTIFS(Figures!$D:$D,$A35,Figures!$K:$K,"QUERY")</f>
-        <v/>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1289,13 +1215,11 @@
       <c r="B36" t="n">
         <v>7</v>
       </c>
-      <c r="C36">
-        <f>COUNTIFS(Figures!$D:$D,$A36,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D36">
-        <f>COUNTIFS(Figures!$D:$D,$A36,Figures!$K:$K,"QUERY")</f>
-        <v/>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1322,13 +1246,11 @@
       <c r="B37" t="n">
         <v>140</v>
       </c>
-      <c r="C37">
-        <f>COUNTIFS(Figures!$D:$D,$A37,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D37">
-        <f>COUNTIFS(Figures!$D:$D,$A37,Figures!$K:$K,"QUERY")</f>
-        <v/>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1355,13 +1277,11 @@
       <c r="B38" t="n">
         <v>2</v>
       </c>
-      <c r="C38">
-        <f>COUNTIFS(Figures!$D:$D,$A38,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D38">
-        <f>COUNTIFS(Figures!$D:$D,$A38,Figures!$K:$K,"QUERY")</f>
-        <v/>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1388,13 +1308,11 @@
       <c r="B39" t="n">
         <v>101</v>
       </c>
-      <c r="C39">
-        <f>COUNTIFS(Figures!$D:$D,$A39,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D39">
-        <f>COUNTIFS(Figures!$D:$D,$A39,Figures!$K:$K,"QUERY")</f>
-        <v/>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1421,13 +1339,11 @@
       <c r="B40" t="n">
         <v>52</v>
       </c>
-      <c r="C40">
-        <f>COUNTIFS(Figures!$D:$D,$A40,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D40">
-        <f>COUNTIFS(Figures!$D:$D,$A40,Figures!$K:$K,"QUERY")</f>
-        <v/>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1454,13 +1370,11 @@
       <c r="B41" t="n">
         <v>2</v>
       </c>
-      <c r="C41">
-        <f>COUNTIFS(Figures!$D:$D,$A41,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D41">
-        <f>COUNTIFS(Figures!$D:$D,$A41,Figures!$K:$K,"QUERY")</f>
-        <v/>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1487,13 +1401,11 @@
       <c r="B42" t="n">
         <v>2</v>
       </c>
-      <c r="C42">
-        <f>COUNTIFS(Figures!$D:$D,$A42,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D42">
-        <f>COUNTIFS(Figures!$D:$D,$A42,Figures!$K:$K,"QUERY")</f>
-        <v/>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1520,13 +1432,11 @@
       <c r="B43" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="C43" s="7">
-        <f>COUNTIFS(Figures!$D:$D,$A43,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D43" s="7">
-        <f>COUNTIFS(Figures!$D:$D,$A43,Figures!$K:$K,"QUERY")</f>
-        <v/>
+      <c r="C43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
@@ -1553,13 +1463,11 @@
       <c r="B44" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="C44" s="7">
-        <f>COUNTIFS(Figures!$D:$D,$A44,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D44" s="7">
-        <f>COUNTIFS(Figures!$D:$D,$A44,Figures!$K:$K,"QUERY")</f>
-        <v/>
+      <c r="C44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
@@ -1586,13 +1494,11 @@
       <c r="B45" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="C45" s="7">
-        <f>COUNTIFS(Figures!$D:$D,$A45,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D45" s="7">
-        <f>COUNTIFS(Figures!$D:$D,$A45,Figures!$K:$K,"QUERY")</f>
-        <v/>
+      <c r="C45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
@@ -1619,13 +1525,11 @@
       <c r="B46" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="C46" s="7">
-        <f>COUNTIFS(Figures!$D:$D,$A46,Figures!$K:$K,"Y")</f>
-        <v/>
-      </c>
-      <c r="D46" s="7">
-        <f>COUNTIFS(Figures!$D:$D,$A46,Figures!$K:$K,"QUERY")</f>
-        <v/>
+      <c r="C46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>

--- a/reference/verification/Labourmax_verification.xlsx
+++ b/reference/verification/Labourmax_verification.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>NOT verified</t>
+          <t>superseded — nothing to check</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1530,11 +1530,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-REMUNERATION</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>dev-loader@labourmax.invalid</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1561,11 +1561,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-RULES-r4</t>
+          <t>REF-2026.03.01-REMUNERATION</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -1592,11 +1592,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-SD1-r4</t>
+          <t>REF-2026.03.01-RULES-r4</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -1623,11 +1623,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-SICK-ACCRUAL</t>
+          <t>REF-2026.03.01-SD1-r4</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-TERMINATION</t>
+          <t>REF-2026.03.01-SICK-ACCRUAL</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1685,11 +1685,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>REF-2026.04.01-BCCCI</t>
+          <t>REF-2026.03.01-TERMINATION</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>superseded — nothing to check</t>
+          <t>NOT verified</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -1716,11 +1716,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>REF-2026.04.01-BCCCI-LEAVE-TYPES</t>
+          <t>REF-2026.04.01-BCCCI</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>NOT verified</t>
+          <t>superseded — nothing to check</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>dev-loader@labourmax.invalid</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -1747,11 +1747,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>REF-2026.04.01-BCCCI-MATERNITY</t>
+          <t>REF-2026.04.01-BCCCI-LEAVE-TYPES</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>superseded — nothing to check</t>
+          <t>NOT verified</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>dev-loader@labourmax.invalid</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -1778,11 +1778,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>REF-2026.04.01-BCCCI-MATERNITY-r2</t>
+          <t>REF-2026.04.01-BCCCI-MATERNITY</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>NOT verified</t>
+          <t>superseded — nothing to check</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -1809,11 +1809,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>REF-2026.04.01-BCCCI-NOTICE-r2</t>
+          <t>REF-2026.04.01-BCCCI-MATERNITY-r2</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>superseded — nothing to check</t>
+          <t>NOT verified</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -1840,11 +1840,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>REF-2026.04.01-BCCCI-NOTICE-r3</t>
+          <t>REF-2026.04.01-BCCCI-NOTICE-r2</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>NOT verified</t>
+          <t>superseded — nothing to check</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -1871,7 +1871,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>REF-2026.04.01-BCCCI-r2</t>
+          <t>REF-2026.04.01-BCCCI-NOTICE-r3</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1902,11 +1902,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>REF-2026.04.01-BCCCI-RULES-r2</t>
+          <t>REF-2026.04.01-BCCCI-r2</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>superseded — nothing to check</t>
+          <t>NOT verified</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -1933,11 +1933,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>REF-2026.04.01-BCCCI-RULES-r3</t>
+          <t>REF-2026.04.01-BCCCI-RULES-r2</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -1947,34 +1947,65 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>superseded — nothing to check</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>dev-loader@labourmax.invalid</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>REF-2026.04.01-BCCCI-RULES-r3</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>8</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>NOT verified</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>dev-loader@labourmax.invalid</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>MACHINE ONLY means verified by claude-verification@labourmax.invalid, which is a development identity and not a person. Those versions need a human pass exactly like the others — they are not done.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Workbook fingerprint</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>d7bf6606bbc67e93</t>
         </is>
@@ -4456,7 +4487,7 @@
           <t>Basic Conditions of Employment Act 75 of 1997</t>
         </is>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>s35, read with Form BCEA1A (Regulation 2), Summary of the Act</t>
         </is>
@@ -5108,11 +5139,15 @@
           <t>Compensation Fund maximum amount of earnings, 2026/2027 assessment year (1 March 2026 - 28 February 2027)</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr"/>
-      <c r="C66" s="10" t="inlineStr"/>
+      <c r="B66" s="9" t="inlineStr"/>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/202604/54577gen3910.pdf</t>
+        </is>
+      </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
@@ -5152,11 +5187,19 @@
           <t>Determination under s6(2) of the Unemployment Insurance Contributions Act 4 of 2002, Government Gazette 44641 of 28 May 2021, effective 1 June 2021</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr"/>
-      <c r="C67" s="10" t="inlineStr"/>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>p. 1</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/202105/44641gon475.pdf</t>
+        </is>
+      </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
@@ -5196,11 +5239,19 @@
           <t>GN 5970, GG 52232, March 2025 (Basic Conditions of Employment Act 75 of 1997, s6(3))</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr"/>
-      <c r="C68" s="10" t="inlineStr"/>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>p. 1</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/202503/52232rg11806gon5970.pdf</t>
+        </is>
+      </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
@@ -5244,11 +5295,15 @@
           <t>GN 7384, GG 54544, 17 April 2026 (Basic Conditions of Employment Act 75 of 1997, s6(3))</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr"/>
-      <c r="C69" s="10" t="inlineStr"/>
+      <c r="B69" s="9" t="inlineStr"/>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>https://www.labour.gov.za/DocumentCenter/Regulations%20and%20Notices/Notices/Basic%20Conditions%20of%20Employment/Basic%20Conditions%20of%20Employment%20Act_Determination%20Earnings%20Threshold2026.pdf</t>
+        </is>
+      </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
@@ -5296,7 +5351,7 @@
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
@@ -5344,7 +5399,7 @@
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
@@ -5388,7 +5443,7 @@
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
@@ -5432,7 +5487,7 @@
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
@@ -5468,15 +5523,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C74" s="10" t="inlineStr"/>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
@@ -5512,15 +5571,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C75" s="14" t="inlineStr"/>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E75" s="14" t="inlineStr">
@@ -5552,15 +5615,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C76" s="14" t="inlineStr"/>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
@@ -5592,15 +5659,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C77" s="14" t="inlineStr"/>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D77" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E77" s="14" t="inlineStr">
@@ -5632,15 +5703,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C78" s="14" t="inlineStr"/>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
@@ -5672,15 +5747,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C79" s="14" t="inlineStr"/>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D79" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E79" s="14" t="inlineStr">
@@ -5712,15 +5791,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C80" s="14" t="inlineStr"/>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
@@ -5752,15 +5835,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C81" s="14" t="inlineStr"/>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D81" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E81" s="14" t="inlineStr">
@@ -5792,15 +5879,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C82" s="14" t="inlineStr"/>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C82" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
@@ -5832,15 +5923,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B83" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C83" s="14" t="inlineStr"/>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C83" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D83" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E83" s="14" t="inlineStr">
@@ -5872,15 +5967,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C84" s="14" t="inlineStr"/>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C84" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
@@ -5912,15 +6011,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B85" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C85" s="14" t="inlineStr"/>
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C85" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D85" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E85" s="14" t="inlineStr">
@@ -5952,15 +6055,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B86" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C86" s="14" t="inlineStr"/>
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C86" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
@@ -5992,15 +6099,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B87" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C87" s="14" t="inlineStr"/>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C87" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D87" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E87" s="14" t="inlineStr">
@@ -6032,15 +6143,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B88" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C88" s="14" t="inlineStr"/>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C88" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
@@ -6072,15 +6187,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B89" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C89" s="14" t="inlineStr"/>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C89" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D89" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E89" s="14" t="inlineStr">
@@ -6112,15 +6231,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B90" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C90" s="14" t="inlineStr"/>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
@@ -6152,15 +6275,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B91" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C91" s="14" t="inlineStr"/>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C91" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D91" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E91" s="14" t="inlineStr">
@@ -6192,15 +6319,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B92" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C92" s="14" t="inlineStr"/>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C92" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
@@ -6232,15 +6363,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B93" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C93" s="14" t="inlineStr"/>
+      <c r="B93" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C93" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D93" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E93" s="14" t="inlineStr">
@@ -6272,15 +6407,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B94" s="12" t="inlineStr">
-        <is>
-          <t>Schedule 1</t>
-        </is>
-      </c>
-      <c r="C94" s="14" t="inlineStr"/>
+      <c r="B94" s="13" t="inlineStr">
+        <is>
+          <t>Schedule 1  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C94" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
@@ -6312,15 +6451,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B95" s="12" t="inlineStr">
+      <c r="B95" s="13" t="inlineStr">
         <is>
           <t>s2(1)</t>
         </is>
       </c>
-      <c r="C95" s="14" t="inlineStr"/>
+      <c r="C95" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D95" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E95" s="14" t="inlineStr">
@@ -6352,15 +6495,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B96" s="12" t="inlineStr">
+      <c r="B96" s="13" t="inlineStr">
         <is>
           <t>s2(1)</t>
         </is>
       </c>
-      <c r="C96" s="14" t="inlineStr"/>
+      <c r="C96" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
@@ -6392,15 +6539,19 @@
           <t>Public Holidays Act 36 of 1994</t>
         </is>
       </c>
-      <c r="B97" s="12" t="inlineStr">
+      <c r="B97" s="13" t="inlineStr">
         <is>
           <t>s2(1)</t>
         </is>
       </c>
-      <c r="C97" s="14" t="inlineStr"/>
+      <c r="C97" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/act36of1994.pdf</t>
+        </is>
+      </c>
       <c r="D97" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E97" s="14" t="inlineStr">
@@ -7284,7 +7435,7 @@
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E119" s="10" t="inlineStr">
@@ -7328,7 +7479,7 @@
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
@@ -7372,7 +7523,7 @@
       </c>
       <c r="D121" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E121" s="14" t="inlineStr">
@@ -7412,7 +7563,7 @@
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
@@ -7452,7 +7603,7 @@
       </c>
       <c r="D123" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E123" s="14" t="inlineStr">
@@ -7492,7 +7643,7 @@
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E124" s="14" t="inlineStr">
@@ -7532,7 +7683,7 @@
       </c>
       <c r="D125" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E125" s="14" t="inlineStr">
@@ -7572,7 +7723,7 @@
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E126" s="14" t="inlineStr">
@@ -7612,7 +7763,7 @@
       </c>
       <c r="D127" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E127" s="14" t="inlineStr">
@@ -7652,7 +7803,7 @@
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E128" s="14" t="inlineStr">
@@ -7692,7 +7843,7 @@
       </c>
       <c r="D129" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E129" s="14" t="inlineStr">
@@ -8576,15 +8727,19 @@
           <t>Skills Development Levies Act 9 of 1999</t>
         </is>
       </c>
-      <c r="B150" s="8" t="inlineStr">
-        <is>
-          <t>s3(1)</t>
-        </is>
-      </c>
-      <c r="C150" s="10" t="inlineStr"/>
+      <c r="B150" s="9" t="inlineStr">
+        <is>
+          <t>s3(1)  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/a9-99.pdf</t>
+        </is>
+      </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E150" s="10" t="inlineStr">
@@ -8624,15 +8779,19 @@
           <t>Skills Development Levies Act 9 of 1999</t>
         </is>
       </c>
-      <c r="B151" s="12" t="inlineStr">
-        <is>
-          <t>s4(b)</t>
-        </is>
-      </c>
-      <c r="C151" s="14" t="inlineStr"/>
+      <c r="B151" s="13" t="inlineStr">
+        <is>
+          <t>s4(b)  [p. 5]</t>
+        </is>
+      </c>
+      <c r="C151" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/a9-99.pdf</t>
+        </is>
+      </c>
       <c r="D151" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E151" s="14" t="inlineStr">
@@ -8668,15 +8827,19 @@
           <t>Unemployment Insurance Contributions Act 4 of 2002</t>
         </is>
       </c>
-      <c r="B152" s="8" t="inlineStr">
-        <is>
-          <t>s6(1)(a)</t>
-        </is>
-      </c>
-      <c r="C152" s="10" t="inlineStr"/>
+      <c r="B152" s="9" t="inlineStr">
+        <is>
+          <t>s6(1)(a)  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/a4-02.pdf</t>
+        </is>
+      </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E152" s="10" t="inlineStr">
@@ -8716,15 +8879,19 @@
           <t>Unemployment Insurance Contributions Act 4 of 2002</t>
         </is>
       </c>
-      <c r="B153" s="12" t="inlineStr">
-        <is>
-          <t>s6(1)(a)(ii)</t>
-        </is>
-      </c>
-      <c r="C153" s="14" t="inlineStr"/>
+      <c r="B153" s="13" t="inlineStr">
+        <is>
+          <t>s6(1)(a)(ii)  [p. 4]</t>
+        </is>
+      </c>
+      <c r="C153" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201409/a4-02.pdf</t>
+        </is>
+      </c>
       <c r="D153" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E153" s="14" t="inlineStr">
@@ -8760,15 +8927,19 @@
           <t>Value-Added Tax Act 89 of 1991</t>
         </is>
       </c>
-      <c r="B154" s="8" t="inlineStr">
+      <c r="B154" s="9" t="inlineStr">
         <is>
           <t>s7(1)(a)</t>
         </is>
       </c>
-      <c r="C154" s="10" t="inlineStr"/>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/sites/default/files/gcis_document/201505/act-89-1991s.pdf</t>
+        </is>
+      </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="E154" s="10" t="inlineStr">
@@ -9048,89 +9219,156 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B129" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B155" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B156" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B157" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B129" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B151" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B152" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B153" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B154" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B155" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B156" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B157" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId224"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22782,7 +23020,7 @@
       <c r="B284" s="12" t="inlineStr"/>
       <c r="C284" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D284" s="14" t="inlineStr">
@@ -22826,7 +23064,7 @@
       <c r="B285" s="12" t="inlineStr"/>
       <c r="C285" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D285" s="14" t="inlineStr">
@@ -22870,7 +23108,7 @@
       <c r="B286" s="12" t="inlineStr"/>
       <c r="C286" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D286" s="14" t="inlineStr">
@@ -22914,7 +23152,7 @@
       <c r="B287" s="12" t="inlineStr"/>
       <c r="C287" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D287" s="14" t="inlineStr">
@@ -22958,7 +23196,7 @@
       <c r="B288" s="12" t="inlineStr"/>
       <c r="C288" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D288" s="14" t="inlineStr">
@@ -23006,7 +23244,7 @@
       <c r="B289" s="12" t="inlineStr"/>
       <c r="C289" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D289" s="14" t="inlineStr">
@@ -23054,7 +23292,7 @@
       <c r="B290" s="12" t="inlineStr"/>
       <c r="C290" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D290" s="14" t="inlineStr">
@@ -23098,7 +23336,7 @@
       <c r="B291" s="12" t="inlineStr"/>
       <c r="C291" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D291" s="14" t="inlineStr">
@@ -23142,7 +23380,7 @@
       <c r="B292" s="12" t="inlineStr"/>
       <c r="C292" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D292" s="14" t="inlineStr">
@@ -23186,7 +23424,7 @@
       <c r="B293" s="12" t="inlineStr"/>
       <c r="C293" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D293" s="14" t="inlineStr">
@@ -23230,7 +23468,7 @@
       <c r="B294" s="12" t="inlineStr"/>
       <c r="C294" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D294" s="14" t="inlineStr">
@@ -23274,7 +23512,7 @@
       <c r="B295" s="12" t="inlineStr"/>
       <c r="C295" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D295" s="14" t="inlineStr">
@@ -23318,7 +23556,7 @@
       <c r="B296" s="12" t="inlineStr"/>
       <c r="C296" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D296" s="14" t="inlineStr">
@@ -23362,7 +23600,7 @@
       <c r="B297" s="12" t="inlineStr"/>
       <c r="C297" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D297" s="14" t="inlineStr">
@@ -23406,7 +23644,7 @@
       <c r="B298" s="12" t="inlineStr"/>
       <c r="C298" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D298" s="14" t="inlineStr">
@@ -23450,7 +23688,7 @@
       <c r="B299" s="12" t="inlineStr"/>
       <c r="C299" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D299" s="14" t="inlineStr">
@@ -23498,7 +23736,7 @@
       </c>
       <c r="C300" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D300" s="14" t="inlineStr">
@@ -23542,7 +23780,7 @@
       </c>
       <c r="C301" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D301" s="14" t="inlineStr">
@@ -23586,7 +23824,7 @@
       </c>
       <c r="C302" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D302" s="14" t="inlineStr">
@@ -23630,7 +23868,7 @@
       </c>
       <c r="C303" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D303" s="14" t="inlineStr">
@@ -23674,7 +23912,7 @@
       </c>
       <c r="C304" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D304" s="14" t="inlineStr">
@@ -23718,7 +23956,7 @@
       </c>
       <c r="C305" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D305" s="14" t="inlineStr">
@@ -23762,7 +24000,7 @@
       </c>
       <c r="C306" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D306" s="14" t="inlineStr">
@@ -23806,7 +24044,7 @@
       </c>
       <c r="C307" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D307" s="14" t="inlineStr">
@@ -23850,7 +24088,7 @@
       </c>
       <c r="C308" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D308" s="14" t="inlineStr">
@@ -23894,7 +24132,7 @@
       </c>
       <c r="C309" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D309" s="14" t="inlineStr">
@@ -23938,7 +24176,7 @@
       </c>
       <c r="C310" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D310" s="14" t="inlineStr">
@@ -23982,7 +24220,7 @@
       </c>
       <c r="C311" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D311" s="14" t="inlineStr">
@@ -24026,7 +24264,7 @@
       </c>
       <c r="C312" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D312" s="14" t="inlineStr">
@@ -24070,7 +24308,7 @@
       </c>
       <c r="C313" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D313" s="14" t="inlineStr">
@@ -24114,7 +24352,7 @@
       </c>
       <c r="C314" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D314" s="14" t="inlineStr">
@@ -24158,7 +24396,7 @@
       </c>
       <c r="C315" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D315" s="14" t="inlineStr">
@@ -24202,7 +24440,7 @@
       </c>
       <c r="C316" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D316" s="14" t="inlineStr">
@@ -24246,7 +24484,7 @@
       </c>
       <c r="C317" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D317" s="14" t="inlineStr">
@@ -24290,7 +24528,7 @@
       </c>
       <c r="C318" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D318" s="14" t="inlineStr">
@@ -24334,7 +24572,7 @@
       </c>
       <c r="C319" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D319" s="14" t="inlineStr">
@@ -24378,7 +24616,7 @@
       </c>
       <c r="C320" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D320" s="14" t="inlineStr">
@@ -24422,7 +24660,7 @@
       </c>
       <c r="C321" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D321" s="14" t="inlineStr">
@@ -24466,7 +24704,7 @@
       </c>
       <c r="C322" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D322" s="14" t="inlineStr">
@@ -24510,7 +24748,7 @@
       </c>
       <c r="C323" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D323" s="14" t="inlineStr">
@@ -24554,7 +24792,7 @@
       </c>
       <c r="C324" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D324" s="14" t="inlineStr">
@@ -24598,7 +24836,7 @@
       </c>
       <c r="C325" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D325" s="14" t="inlineStr">
@@ -24642,7 +24880,7 @@
       </c>
       <c r="C326" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D326" s="14" t="inlineStr">
@@ -24686,7 +24924,7 @@
       </c>
       <c r="C327" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D327" s="14" t="inlineStr">
@@ -24730,7 +24968,7 @@
       </c>
       <c r="C328" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D328" s="14" t="inlineStr">
@@ -24774,7 +25012,7 @@
       </c>
       <c r="C329" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D329" s="14" t="inlineStr">
@@ -24818,7 +25056,7 @@
       </c>
       <c r="C330" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D330" s="14" t="inlineStr">
@@ -24862,7 +25100,7 @@
       </c>
       <c r="C331" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D331" s="14" t="inlineStr">
@@ -24906,7 +25144,7 @@
       </c>
       <c r="C332" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D332" s="14" t="inlineStr">
@@ -24950,7 +25188,7 @@
       </c>
       <c r="C333" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D333" s="14" t="inlineStr">
@@ -24994,7 +25232,7 @@
       </c>
       <c r="C334" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D334" s="14" t="inlineStr">
@@ -25038,7 +25276,7 @@
       </c>
       <c r="C335" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D335" s="14" t="inlineStr">
@@ -25082,7 +25320,7 @@
       </c>
       <c r="C336" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D336" s="14" t="inlineStr">
@@ -25126,7 +25364,7 @@
       </c>
       <c r="C337" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D337" s="14" t="inlineStr">
@@ -25170,7 +25408,7 @@
       </c>
       <c r="C338" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D338" s="14" t="inlineStr">
@@ -25214,7 +25452,7 @@
       </c>
       <c r="C339" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D339" s="14" t="inlineStr">
@@ -25258,7 +25496,7 @@
       </c>
       <c r="C340" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D340" s="14" t="inlineStr">
@@ -25302,7 +25540,7 @@
       </c>
       <c r="C341" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D341" s="14" t="inlineStr">
@@ -25346,7 +25584,7 @@
       </c>
       <c r="C342" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D342" s="14" t="inlineStr">
@@ -25390,7 +25628,7 @@
       </c>
       <c r="C343" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D343" s="14" t="inlineStr">
@@ -25434,7 +25672,7 @@
       </c>
       <c r="C344" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D344" s="14" t="inlineStr">
@@ -25478,7 +25716,7 @@
       </c>
       <c r="C345" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D345" s="14" t="inlineStr">
@@ -25522,7 +25760,7 @@
       </c>
       <c r="C346" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D346" s="14" t="inlineStr">
@@ -25566,7 +25804,7 @@
       </c>
       <c r="C347" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D347" s="14" t="inlineStr">
@@ -25610,7 +25848,7 @@
       </c>
       <c r="C348" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D348" s="14" t="inlineStr">
@@ -25654,7 +25892,7 @@
       </c>
       <c r="C349" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D349" s="14" t="inlineStr">
@@ -25698,7 +25936,7 @@
       </c>
       <c r="C350" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D350" s="14" t="inlineStr">
@@ -25742,7 +25980,7 @@
       </c>
       <c r="C351" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D351" s="14" t="inlineStr">
@@ -25786,7 +26024,7 @@
       </c>
       <c r="C352" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D352" s="14" t="inlineStr">
@@ -25830,7 +26068,7 @@
       </c>
       <c r="C353" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D353" s="14" t="inlineStr">
@@ -25874,7 +26112,7 @@
       </c>
       <c r="C354" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D354" s="14" t="inlineStr">
@@ -25918,7 +26156,7 @@
       </c>
       <c r="C355" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D355" s="14" t="inlineStr">
@@ -25962,7 +26200,7 @@
       </c>
       <c r="C356" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D356" s="14" t="inlineStr">
@@ -26006,7 +26244,7 @@
       </c>
       <c r="C357" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D357" s="14" t="inlineStr">
@@ -26050,7 +26288,7 @@
       </c>
       <c r="C358" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D358" s="14" t="inlineStr">
@@ -26094,7 +26332,7 @@
       </c>
       <c r="C359" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D359" s="14" t="inlineStr">
@@ -26138,7 +26376,7 @@
       </c>
       <c r="C360" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D360" s="14" t="inlineStr">
@@ -26182,7 +26420,7 @@
       </c>
       <c r="C361" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D361" s="14" t="inlineStr">
@@ -26226,7 +26464,7 @@
       </c>
       <c r="C362" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D362" s="14" t="inlineStr">
@@ -26270,7 +26508,7 @@
       </c>
       <c r="C363" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D363" s="14" t="inlineStr">
@@ -26314,7 +26552,7 @@
       </c>
       <c r="C364" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D364" s="14" t="inlineStr">
@@ -26358,7 +26596,7 @@
       </c>
       <c r="C365" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D365" s="14" t="inlineStr">
@@ -26402,7 +26640,7 @@
       </c>
       <c r="C366" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D366" s="14" t="inlineStr">
@@ -26446,7 +26684,7 @@
       </c>
       <c r="C367" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D367" s="14" t="inlineStr">
@@ -26490,7 +26728,7 @@
       </c>
       <c r="C368" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D368" s="14" t="inlineStr">
@@ -26534,7 +26772,7 @@
       </c>
       <c r="C369" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D369" s="14" t="inlineStr">
@@ -26578,7 +26816,7 @@
       </c>
       <c r="C370" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D370" s="14" t="inlineStr">
@@ -26622,7 +26860,7 @@
       </c>
       <c r="C371" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D371" s="14" t="inlineStr">
@@ -26666,7 +26904,7 @@
       </c>
       <c r="C372" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D372" s="14" t="inlineStr">
@@ -26710,7 +26948,7 @@
       </c>
       <c r="C373" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D373" s="14" t="inlineStr">
@@ -26754,7 +26992,7 @@
       </c>
       <c r="C374" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D374" s="14" t="inlineStr">
@@ -31834,7 +32072,7 @@
       <c r="B501" s="12" t="inlineStr"/>
       <c r="C501" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D501" s="14" t="inlineStr">
@@ -31874,7 +32112,7 @@
       <c r="B502" s="12" t="inlineStr"/>
       <c r="C502" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D502" s="14" t="inlineStr">
@@ -31914,7 +32152,7 @@
       <c r="B503" s="12" t="inlineStr"/>
       <c r="C503" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D503" s="14" t="inlineStr">
@@ -31954,7 +32192,7 @@
       <c r="B504" s="12" t="inlineStr"/>
       <c r="C504" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D504" s="14" t="inlineStr">
@@ -31994,7 +32232,7 @@
       <c r="B505" s="12" t="inlineStr"/>
       <c r="C505" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D505" s="14" t="inlineStr">
@@ -32034,7 +32272,7 @@
       <c r="B506" s="12" t="inlineStr"/>
       <c r="C506" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D506" s="14" t="inlineStr">
@@ -32074,7 +32312,7 @@
       <c r="B507" s="12" t="inlineStr"/>
       <c r="C507" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D507" s="14" t="inlineStr">
@@ -32114,7 +32352,7 @@
       <c r="B508" s="12" t="inlineStr"/>
       <c r="C508" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D508" s="14" t="inlineStr">
@@ -32154,7 +32392,7 @@
       <c r="B509" s="12" t="inlineStr"/>
       <c r="C509" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D509" s="14" t="inlineStr">
@@ -32194,7 +32432,7 @@
       <c r="B510" s="12" t="inlineStr"/>
       <c r="C510" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D510" s="14" t="inlineStr">
@@ -32234,7 +32472,7 @@
       <c r="B511" s="12" t="inlineStr"/>
       <c r="C511" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D511" s="14" t="inlineStr">
@@ -32274,7 +32512,7 @@
       <c r="B512" s="12" t="inlineStr"/>
       <c r="C512" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D512" s="14" t="inlineStr">
@@ -32314,7 +32552,7 @@
       <c r="B513" s="12" t="inlineStr"/>
       <c r="C513" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D513" s="14" t="inlineStr">
@@ -32354,7 +32592,7 @@
       <c r="B514" s="12" t="inlineStr"/>
       <c r="C514" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D514" s="14" t="inlineStr">
@@ -32394,7 +32632,7 @@
       <c r="B515" s="12" t="inlineStr"/>
       <c r="C515" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D515" s="14" t="inlineStr">
@@ -32434,7 +32672,7 @@
       <c r="B516" s="12" t="inlineStr"/>
       <c r="C516" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D516" s="14" t="inlineStr">
@@ -32474,7 +32712,7 @@
       <c r="B517" s="12" t="inlineStr"/>
       <c r="C517" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D517" s="14" t="inlineStr">
@@ -32514,7 +32752,7 @@
       <c r="B518" s="12" t="inlineStr"/>
       <c r="C518" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D518" s="14" t="inlineStr">
@@ -32554,7 +32792,7 @@
       <c r="B519" s="12" t="inlineStr"/>
       <c r="C519" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D519" s="14" t="inlineStr">
@@ -32594,7 +32832,7 @@
       <c r="B520" s="12" t="inlineStr"/>
       <c r="C520" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D520" s="14" t="inlineStr">
@@ -32634,7 +32872,7 @@
       <c r="B521" s="12" t="inlineStr"/>
       <c r="C521" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D521" s="14" t="inlineStr">
@@ -32674,7 +32912,7 @@
       <c r="B522" s="12" t="inlineStr"/>
       <c r="C522" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D522" s="14" t="inlineStr">
@@ -32714,7 +32952,7 @@
       <c r="B523" s="12" t="inlineStr"/>
       <c r="C523" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D523" s="14" t="inlineStr">
@@ -32754,7 +32992,7 @@
       <c r="B524" s="12" t="inlineStr"/>
       <c r="C524" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D524" s="14" t="inlineStr">
@@ -32794,7 +33032,7 @@
       <c r="B525" s="12" t="inlineStr"/>
       <c r="C525" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D525" s="14" t="inlineStr">
@@ -32834,7 +33072,7 @@
       <c r="B526" s="12" t="inlineStr"/>
       <c r="C526" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D526" s="14" t="inlineStr">
@@ -32874,7 +33112,7 @@
       <c r="B527" s="12" t="inlineStr"/>
       <c r="C527" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D527" s="14" t="inlineStr">
@@ -32914,7 +33152,7 @@
       <c r="B528" s="12" t="inlineStr"/>
       <c r="C528" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D528" s="14" t="inlineStr">
@@ -32954,7 +33192,7 @@
       <c r="B529" s="12" t="inlineStr"/>
       <c r="C529" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D529" s="14" t="inlineStr">
@@ -32994,7 +33232,7 @@
       <c r="B530" s="12" t="inlineStr"/>
       <c r="C530" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D530" s="14" t="inlineStr">
@@ -33034,7 +33272,7 @@
       <c r="B531" s="12" t="inlineStr"/>
       <c r="C531" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D531" s="14" t="inlineStr">
@@ -33074,7 +33312,7 @@
       <c r="B532" s="12" t="inlineStr"/>
       <c r="C532" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D532" s="14" t="inlineStr">
@@ -33114,7 +33352,7 @@
       <c r="B533" s="12" t="inlineStr"/>
       <c r="C533" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D533" s="14" t="inlineStr">
@@ -33154,7 +33392,7 @@
       <c r="B534" s="12" t="inlineStr"/>
       <c r="C534" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D534" s="14" t="inlineStr">
@@ -33194,7 +33432,7 @@
       <c r="B535" s="12" t="inlineStr"/>
       <c r="C535" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D535" s="14" t="inlineStr">
@@ -33234,7 +33472,7 @@
       <c r="B536" s="12" t="inlineStr"/>
       <c r="C536" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D536" s="14" t="inlineStr">
@@ -33274,7 +33512,7 @@
       <c r="B537" s="12" t="inlineStr"/>
       <c r="C537" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D537" s="14" t="inlineStr">
@@ -33314,7 +33552,7 @@
       <c r="B538" s="12" t="inlineStr"/>
       <c r="C538" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D538" s="14" t="inlineStr">
@@ -33354,7 +33592,7 @@
       <c r="B539" s="12" t="inlineStr"/>
       <c r="C539" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D539" s="14" t="inlineStr">
@@ -39566,7 +39804,7 @@
       </c>
       <c r="C673" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D673" s="14" t="inlineStr">
@@ -39614,7 +39852,7 @@
       </c>
       <c r="C674" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D674" s="14" t="inlineStr">
@@ -39662,7 +39900,7 @@
       </c>
       <c r="C675" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D675" s="14" t="inlineStr">
@@ -39710,7 +39948,7 @@
       </c>
       <c r="C676" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D676" s="14" t="inlineStr">
@@ -39758,7 +39996,7 @@
       </c>
       <c r="C677" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D677" s="14" t="inlineStr">
@@ -39806,7 +40044,7 @@
       </c>
       <c r="C678" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D678" s="14" t="inlineStr">
@@ -39854,7 +40092,7 @@
       </c>
       <c r="C679" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D679" s="14" t="inlineStr">
@@ -39902,7 +40140,7 @@
       </c>
       <c r="C680" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D680" s="14" t="inlineStr">
@@ -39950,7 +40188,7 @@
       </c>
       <c r="C681" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D681" s="14" t="inlineStr">
@@ -39998,7 +40236,7 @@
       </c>
       <c r="C682" s="14" t="inlineStr">
         <is>
-          <t>REF-2026.03.01-r2</t>
+          <t>REF-2026.03.01-r3</t>
         </is>
       </c>
       <c r="D682" s="14" t="inlineStr">

--- a/reference/verification/Labourmax_verification.xlsx
+++ b/reference/verification/Labourmax_verification.xlsx
@@ -21,9 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="8">
     <font>
       <name val="Calibri"/>
@@ -93,7 +91,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -122,7 +120,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2517,6 +2514,7 @@
           <t>2026-09-21</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -2580,6 +2578,7 @@
           <t>2026-09-21</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -2643,6 +2642,7 @@
           <t>2026-09-21</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -2774,6 +2774,7 @@
           <t>2026-09-21</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -2837,6 +2838,7 @@
           <t>2026-09-21</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -2892,6 +2894,7 @@
           <t>2026-09-22</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -2947,6 +2950,7 @@
           <t>2026-09-21</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -3002,6 +3006,7 @@
           <t>2026-09-22</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -3313,6 +3318,7 @@
           <t>2026-09-21</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
@@ -3380,6 +3386,7 @@
           <t>2026-09-21</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
@@ -3447,6 +3454,7 @@
           <t>2026-09-21</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
@@ -3510,6 +3518,7 @@
           <t>2026-09-21</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
@@ -3569,6 +3578,7 @@
           <t>2026-09-21</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
@@ -3628,6 +3638,7 @@
           <t>2026-09-21</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
@@ -6312,11 +6323,7 @@
           <t>Compensation Fund maximum amount of earnings, 2026/2027 assessment year (1 March 2026 - 28 February 2027)</t>
         </is>
       </c>
-      <c r="B74" s="10" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/Compensation-Fund-maximum-amount-of-earnings_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B74" s="10" t="inlineStr"/>
       <c r="C74" s="10" t="inlineStr">
         <is>
           <t>https://www.gov.za/sites/default/files/gcis_document/202604/54577gen3910.pdf</t>
@@ -6500,11 +6507,7 @@
           <t>GN 7384, GG 54544, 17 April 2026 (Basic Conditions of Employment Act 75 of 1997, s6(3))</t>
         </is>
       </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/GN-7384_GN7384_GG54544_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B77" s="10" t="inlineStr"/>
       <c r="C77" s="10" t="inlineStr">
         <is>
           <t>https://www.labour.gov.za/DocumentCenter/Regulations%20and%20Notices/Notices/Basic%20Conditions%20of%20Employment/Basic%20Conditions%20of%20Employment%20Act_Determination%20Earnings%20Threshold2026.pdf</t>
@@ -6568,11 +6571,7 @@
           <t>GN R.7083, GG 54075, 3 February 2026 (National Minimum Wage Act 9 of 2018)</t>
         </is>
       </c>
-      <c r="B78" s="10" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/GN-R-7083_GN7083_GG54075_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B78" s="10" t="inlineStr"/>
       <c r="C78" s="10" t="inlineStr">
         <is>
           <t>https://www.gov.za/sites/default/files/gcis_document/202602/54075rg11941gon7083.pdf</t>
@@ -6632,11 +6631,7 @@
           <t>GN R.7083, GG 54075, 3 February 2026 (National Minimum Wage Act 9 of 2018)</t>
         </is>
       </c>
-      <c r="B79" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/GN-R-7083_GN7083_GG54075_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B79" s="14" t="inlineStr"/>
       <c r="C79" s="14" t="inlineStr">
         <is>
           <t>https://www.gov.za/sites/default/files/gcis_document/202602/54075rg11941gon7083.pdf</t>
@@ -6685,11 +6680,7 @@
           <t>GN R.7083, GG 54075, 3 February 2026 (National Minimum Wage Act 9 of 2018)</t>
         </is>
       </c>
-      <c r="B80" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/GN-R-7083_GN7083_GG54075_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B80" s="14" t="inlineStr"/>
       <c r="C80" s="14" t="inlineStr">
         <is>
           <t>https://www.gov.za/sites/default/files/gcis_document/202602/54075rg11941gon7083.pdf</t>
@@ -6738,11 +6729,7 @@
           <t>GN R.7083, GG 54075, 3 February 2026 (National Minimum Wage Act 9 of 2018)</t>
         </is>
       </c>
-      <c r="B81" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/GN-R-7083_GN7083_GG54075_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B81" s="14" t="inlineStr"/>
       <c r="C81" s="14" t="inlineStr">
         <is>
           <t>https://www.gov.za/sites/default/files/gcis_document/202602/54075rg11941gon7083.pdf</t>
@@ -8176,6 +8163,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
@@ -8183,11 +8171,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B110" s="10" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B110" s="10" t="inlineStr"/>
       <c r="C110" s="10" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -8243,11 +8227,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B111" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B111" s="14" t="inlineStr"/>
       <c r="C111" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -8295,6 +8275,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
@@ -8302,11 +8283,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B112" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B112" s="14" t="inlineStr"/>
       <c r="C112" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -8354,6 +8331,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="13" t="inlineStr">
@@ -8361,11 +8339,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B113" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B113" s="14" t="inlineStr"/>
       <c r="C113" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -8413,6 +8387,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
@@ -8420,11 +8395,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B114" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B114" s="14" t="inlineStr"/>
       <c r="C114" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -8472,6 +8443,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="13" t="inlineStr">
@@ -8479,11 +8451,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B115" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B115" s="14" t="inlineStr"/>
       <c r="C115" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -8531,6 +8499,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
@@ -8538,11 +8507,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B116" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B116" s="14" t="inlineStr"/>
       <c r="C116" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -8590,6 +8555,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="13" t="inlineStr">
@@ -8597,11 +8563,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B117" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B117" s="14" t="inlineStr"/>
       <c r="C117" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -8649,6 +8611,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
@@ -8656,11 +8619,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B118" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B118" s="14" t="inlineStr"/>
       <c r="C118" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -8708,6 +8667,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="13" t="inlineStr">
@@ -8715,11 +8675,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B119" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B119" s="14" t="inlineStr"/>
       <c r="C119" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -8767,6 +8723,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
@@ -8774,11 +8731,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B120" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B120" s="14" t="inlineStr"/>
       <c r="C120" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -8826,6 +8779,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="13" t="inlineStr">
@@ -8833,11 +8787,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B121" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B121" s="14" t="inlineStr"/>
       <c r="C121" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -8885,6 +8835,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
@@ -8892,11 +8843,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B122" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B122" s="14" t="inlineStr"/>
       <c r="C122" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -8944,6 +8891,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="13" t="inlineStr">
@@ -8951,11 +8899,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B123" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B123" s="14" t="inlineStr"/>
       <c r="C123" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -9003,6 +8947,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
@@ -9010,11 +8955,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B124" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B124" s="14" t="inlineStr"/>
       <c r="C124" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -9062,6 +9003,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="13" t="inlineStr">
@@ -9069,11 +9011,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B125" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B125" s="14" t="inlineStr"/>
       <c r="C125" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -9121,6 +9059,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
@@ -9128,11 +9067,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B126" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B126" s="14" t="inlineStr"/>
       <c r="C126" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -9180,6 +9115,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="13" t="inlineStr">
@@ -9187,11 +9123,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B127" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B127" s="14" t="inlineStr"/>
       <c r="C127" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -9239,6 +9171,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
@@ -9246,11 +9179,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B128" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B128" s="14" t="inlineStr"/>
       <c r="C128" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -9298,6 +9227,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="13" t="inlineStr">
@@ -9305,11 +9235,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B129" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B129" s="14" t="inlineStr"/>
       <c r="C129" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -9357,6 +9283,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
@@ -9364,11 +9291,7 @@
           <t>SARS Guide for Codes Applicable to Employees Tax Certificates (PAYE-AE-06-G06), 2026 issue, revision 13 effective 19 September 2025</t>
         </is>
       </c>
-      <c r="B130" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Guide-for-Codes-Applicable-to-Employees-Tax-Certifi_PAYE-AE-06-G06_2026.pdf</t>
-        </is>
-      </c>
+      <c r="B130" s="14" t="inlineStr"/>
       <c r="C130" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/wp-content/uploads/Ops/Guides/PAYE-AE-06-G06-Guide-for-Codes-Applicable-to-Employees-Tax-Certificates-2026-External-Guide.pdf</t>
@@ -9416,6 +9339,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
@@ -9423,11 +9347,7 @@
           <t>SARS Medical Tax Credit Rates, 2027 tax year (1 March 2026 - 28 February 2027)</t>
         </is>
       </c>
-      <c r="B131" s="10" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Medical-Tax-Credit-Rates_2027.html</t>
-        </is>
-      </c>
+      <c r="B131" s="10" t="inlineStr"/>
       <c r="C131" s="10" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/tax-rates/medical-tax-credit-rates/</t>
@@ -9487,11 +9407,7 @@
           <t>SARS Rates of Tax for Individuals, 2027 tax year (1 March 2026 - 28 February 2027)</t>
         </is>
       </c>
-      <c r="B132" s="10" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Rates-of-Tax-for-Individuals_2027.html</t>
-        </is>
-      </c>
+      <c r="B132" s="10" t="inlineStr"/>
       <c r="C132" s="10" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/tax-rates/income-tax/rates-of-tax-for-individuals/</t>
@@ -9547,11 +9463,7 @@
           <t>SARS Rates of Tax for Individuals, 2027 tax year (1 March 2026 - 28 February 2027)</t>
         </is>
       </c>
-      <c r="B133" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Rates-of-Tax-for-Individuals_2027.html</t>
-        </is>
-      </c>
+      <c r="B133" s="14" t="inlineStr"/>
       <c r="C133" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/tax-rates/income-tax/rates-of-tax-for-individuals/</t>
@@ -9599,6 +9511,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
@@ -9606,11 +9519,7 @@
           <t>SARS Rates of Tax for Individuals, 2027 tax year (1 March 2026 - 28 February 2027)</t>
         </is>
       </c>
-      <c r="B134" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Rates-of-Tax-for-Individuals_2027.html</t>
-        </is>
-      </c>
+      <c r="B134" s="14" t="inlineStr"/>
       <c r="C134" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/tax-rates/income-tax/rates-of-tax-for-individuals/</t>
@@ -9658,6 +9567,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="13" t="inlineStr">
@@ -9665,11 +9575,7 @@
           <t>SARS Rates of Tax for Individuals, 2027 tax year (1 March 2026 - 28 February 2027)</t>
         </is>
       </c>
-      <c r="B135" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Rates-of-Tax-for-Individuals_2027.html</t>
-        </is>
-      </c>
+      <c r="B135" s="14" t="inlineStr"/>
       <c r="C135" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/tax-rates/income-tax/rates-of-tax-for-individuals/</t>
@@ -9717,6 +9623,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
@@ -9724,11 +9631,7 @@
           <t>SARS Rates of Tax for Individuals, 2027 tax year (1 March 2026 - 28 February 2027)</t>
         </is>
       </c>
-      <c r="B136" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Rates-of-Tax-for-Individuals_2027.html</t>
-        </is>
-      </c>
+      <c r="B136" s="14" t="inlineStr"/>
       <c r="C136" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/tax-rates/income-tax/rates-of-tax-for-individuals/</t>
@@ -9788,11 +9691,7 @@
           <t>SARS Rates of Tax for Individuals, 2027 tax year (1 March 2026 - 28 February 2027)</t>
         </is>
       </c>
-      <c r="B137" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Rates-of-Tax-for-Individuals_2027.html</t>
-        </is>
-      </c>
+      <c r="B137" s="14" t="inlineStr"/>
       <c r="C137" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/tax-rates/income-tax/rates-of-tax-for-individuals/</t>
@@ -9852,11 +9751,7 @@
           <t>SARS Rates of Tax for Individuals, 2027 tax year (1 March 2026 - 28 February 2027)</t>
         </is>
       </c>
-      <c r="B138" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Rates-of-Tax-for-Individuals_2027.html</t>
-        </is>
-      </c>
+      <c r="B138" s="14" t="inlineStr"/>
       <c r="C138" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/tax-rates/income-tax/rates-of-tax-for-individuals/</t>
@@ -9916,11 +9811,7 @@
           <t>SARS Rates of Tax for Individuals, 2027 tax year (1 March 2026 - 28 February 2027)</t>
         </is>
       </c>
-      <c r="B139" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Rates-of-Tax-for-Individuals_2027.html</t>
-        </is>
-      </c>
+      <c r="B139" s="14" t="inlineStr"/>
       <c r="C139" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/tax-rates/income-tax/rates-of-tax-for-individuals/</t>
@@ -9980,11 +9871,7 @@
           <t>SARS Rates of Tax for Individuals, 2027 tax year (1 March 2026 - 28 February 2027)</t>
         </is>
       </c>
-      <c r="B140" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Rates-of-Tax-for-Individuals_2027.html</t>
-        </is>
-      </c>
+      <c r="B140" s="14" t="inlineStr"/>
       <c r="C140" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/tax-rates/income-tax/rates-of-tax-for-individuals/</t>
@@ -10044,11 +9931,7 @@
           <t>SARS Rates of Tax for Individuals, 2027 tax year (1 March 2026 - 28 February 2027)</t>
         </is>
       </c>
-      <c r="B141" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/SARS-Rates-of-Tax-for-Individuals_2027.html</t>
-        </is>
-      </c>
+      <c r="B141" s="14" t="inlineStr"/>
       <c r="C141" s="14" t="inlineStr">
         <is>
           <t>https://www.sars.gov.za/tax-rates/income-tax/rates-of-tax-for-individuals/</t>
@@ -10212,6 +10095,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
@@ -10267,6 +10151,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="13" t="inlineStr">
@@ -10326,6 +10211,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
@@ -10385,6 +10271,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="13" t="inlineStr">
@@ -10444,6 +10331,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
@@ -10503,6 +10391,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="13" t="inlineStr">
@@ -10562,6 +10451,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
@@ -10621,6 +10511,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="13" t="inlineStr">
@@ -10680,6 +10571,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
@@ -10687,11 +10579,7 @@
           <t>Sectoral Determination 7: Domestic Worker Sector, GN R.1068 in RG 7434 (GG 23732), 15 August 2002</t>
         </is>
       </c>
-      <c r="B152" s="10" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/Sectoral-Determination-7-Domestic-Worker-Sector_GN1068_GG23732_2002.pdf</t>
-        </is>
-      </c>
+      <c r="B152" s="10" t="inlineStr"/>
       <c r="C152" s="10" t="inlineStr">
         <is>
           <t>https://static.pmg.org.za/docs/100824gazette_0.pdf</t>
@@ -10755,11 +10643,7 @@
           <t>Sectoral Determination 7: Domestic Worker Sector, GN R.1068 in RG 7434 (GG 23732), 15 August 2002</t>
         </is>
       </c>
-      <c r="B153" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/Sectoral-Determination-7-Domestic-Worker-Sector_GN1068_GG23732_2002.pdf</t>
-        </is>
-      </c>
+      <c r="B153" s="14" t="inlineStr"/>
       <c r="C153" s="14" t="inlineStr">
         <is>
           <t>https://static.pmg.org.za/docs/100824gazette_0.pdf</t>
@@ -10811,6 +10695,7 @@
           <t>2026-09-22</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
@@ -10818,11 +10703,7 @@
           <t>Sectoral Determination 7: Domestic Worker Sector, GN R.1068 in RG 7434 (GG 23732), 15 August 2002</t>
         </is>
       </c>
-      <c r="B154" s="14" t="inlineStr">
-        <is>
-          <t>file:///C:/projects/LabourMax-HR/reference/sources/Sectoral-Determination-7-Domestic-Worker-Sector_GN1068_GG23732_2002.pdf</t>
-        </is>
-      </c>
+      <c r="B154" s="14" t="inlineStr"/>
       <c r="C154" s="14" t="inlineStr">
         <is>
           <t>https://static.pmg.org.za/docs/100824gazette_0.pdf</t>
@@ -10874,6 +10755,7 @@
           <t>2026-09-22</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="13" t="inlineStr">
@@ -10937,6 +10819,7 @@
           <t>2026-09-22</t>
         </is>
       </c>
+      <c r="N155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
@@ -10996,6 +10879,7 @@
           <t>2026-09-22</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="13" t="inlineStr">
@@ -11055,6 +10939,7 @@
           <t>2026-09-22</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
@@ -11114,6 +10999,7 @@
           <t>2026-09-22</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="13" t="inlineStr">
@@ -11177,6 +11063,7 @@
           <t>2026-09-22</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
@@ -11240,6 +11127,7 @@
           <t>2026-09-22</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="13" t="inlineStr">
@@ -11303,6 +11191,7 @@
           <t>2026-09-22</t>
         </is>
       </c>
+      <c r="N161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
@@ -11430,6 +11319,7 @@
           <t>2026-09-22</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
@@ -11557,6 +11447,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
@@ -11756,6 +11647,7 @@
           <t>2026-09-22</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="13" t="inlineStr">
@@ -11804,18 +11696,10 @@
           <t>grp:adoption_age_limit:2:1</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>barkofs@gmail.com</t>
         </is>
-      </c>
-      <c r="M169" s="16" t="n">
-        <v>46287</v>
       </c>
     </row>
   </sheetData>
@@ -11829,8 +11713,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="K2:K169" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Y, N or QUERY" error="Y: every figure on this row matches the document. N: not yet. QUERY: one or more is wrong - say which in Note." type="list">
-      <formula1>"Y,N,QUERY"</formula1>
+    <dataValidation sqref="K2:K169" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Y or QUERY" error="Y: every figure on this row matches the document. QUERY: one or more is wrong - say which in Note. Leave it blank for not yet." type="list">
+      <formula1>"Y,QUERY"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
